--- a/data/opdracht_template_full.xlsx
+++ b/data/opdracht_template_full.xlsx
@@ -597,7 +597,7 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2024-07-24 09:00:02.668729</t>
+    <t>2024-07-24 09:03:33.473416</t>
   </si>
   <si>
     <t>version</t>
